--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B243607E-D19B-48A9-928C-493B175D778C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9708C4-92DE-4163-8B49-CD009B3318E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -155,6 +155,10 @@
 用于解决条件选项问题
 1为正常对话
 2是选项对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练开局对话</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -952,7 +956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B17" s="9">
         <v>1004002</v>
       </c>
@@ -975,18 +979,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="3">
+        <v>1005001</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -997,7 +1016,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9708C4-92DE-4163-8B49-CD009B3318E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1893CB-5FC4-49C6-B068-2593F6AA5917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -159,6 +159,10 @@
   </si>
   <si>
     <t>教练开局对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练拳击馆对话</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1006,15 +1010,30 @@
       </c>
     </row>
     <row r="19" spans="2:11" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="B19" s="5">
+        <v>1006001</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5">
+        <v>2</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B20" s="6"/>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1893CB-5FC4-49C6-B068-2593F6AA5917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDBBCEA-854C-4550-ADDB-CBCFF44BFE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -165,12 +165,47 @@
     <t>教练拳击馆对话</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>教练拳击馆第二轮对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么都没找到</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到牙了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到了报道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1007003|1007004|1007005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我什么都没拿到</t>
+  </si>
+  <si>
+    <t>我找到牙了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我找到了这份报道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|23|24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +215,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -212,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -240,6 +283,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -543,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
@@ -1035,16 +1084,143 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+    <row r="20" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="3">
+        <v>1007001</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1007002</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="3">
+        <v>1007002</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="3">
+        <v>1007003</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="3">
+        <v>1007004</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="3">
+        <v>1007005</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2</v>
+      </c>
+      <c r="I24" s="8">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="5" min="1" max="1"/>
@@ -605,17 +605,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>每个对话类型的不同参数代表不同的作用
-用于解决条件选项问题
-1为正常对话
-2是选项对话</t>
+          <t>0/1.线性对话\n2.选项对话\n3.进入战斗（param2=battle表ID，播完这条对话直接进战斗）</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>当对话类型为选项时：
-1代表普通对话
-2代表动作对话</t>
+          <t>param2：type=3 时填写 battle 表 id</t>
         </is>
       </c>
     </row>
@@ -1256,6 +1251,81 @@
         <v>2</v>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>9001002</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>9001003|9001004</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>9001003</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>打一场</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>9001004</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>算了</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
